--- a/Datas/ManufactureData.xlsx
+++ b/Datas/ManufactureData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -58,6 +58,9 @@
   <si>
     <t>4001,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defaultProduceTime</t>
   </si>
 </sst>
 </file>
@@ -383,14 +386,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:E4"/>
+  <dimension ref="A2:F4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.625" customWidth="1"/>
-    <col min="5" max="5" width="76.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="12.875" customWidth="1"/>
+    <col min="5" max="5" width="19.125" customWidth="1"/>
+    <col min="6" max="6" width="76.875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -403,11 +408,14 @@
       <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -420,11 +428,14 @@
       <c r="D3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>5001</v>
       </c>
@@ -435,9 +446,12 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1021</v>
-      </c>
-      <c r="E4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
     </row>

--- a/Datas/ManufactureData.xlsx
+++ b/Datas/ManufactureData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,13 +61,49 @@
   </si>
   <si>
     <t>defaultProduceTime</t>
+  </si>
+  <si>
+    <t>搅拌器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烘烤炉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>蒸煮锅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>绘写台</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>酿造桶</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>纺织机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>锻造炉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>磨坊</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>劈柴墩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -79,6 +115,13 @@
       <sz val="9"/>
       <name val="等线"/>
       <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -103,9 +146,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -386,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F4"/>
+  <dimension ref="A2:F13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.625" customWidth="1"/>
@@ -455,6 +501,186 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>5002</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>5003</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>5004</v>
+      </c>
+      <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>10</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>5005</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>5006</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>5007</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>10</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>5008</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>10</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>5009</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>10</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>5010</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/ManufactureData.xlsx
+++ b/Datas/ManufactureData.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="ManufactureData" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -96,6 +97,33 @@
   </si>
   <si>
     <t>劈柴墩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3011,0|3100,0|3101,0|3102,0|3103,0|3107,0|3111,0|3115,0|3116,0|3139,0|3168,0|3171,0|3174,0|3175,0|3177,0|3178,0</t>
+  </si>
+  <si>
+    <t>3104,0|3109,0|3117,0|3118,0|3132,0|3133,0|3135,0|3136,0|3166,0|3167,0|3169,0|3170,0|3172,0|3173,0|3176,0</t>
+  </si>
+  <si>
+    <t>3105,0|3106,0|3108,0|3110,0|3112,0|3113,0|3114,0|3119,0|3128,0|3131,0|3134,0|3150,0|3151,0|3152,0|3153,0|3154,0|3155,0|3156,0|3157,0|3158,0|3159,0|3160,0|3161,0|3162,0|3163,0|3164,0|3165,0</t>
+  </si>
+  <si>
+    <t>3130,0|3142,0|3143,0|3144,0|3145,0|3146,0|3147,0|3148,0|3149,0</t>
+  </si>
+  <si>
+    <t>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0|3126,0|3127,0|3129,0|3137,0|3138,0|3140,0|3141,0</t>
+  </si>
+  <si>
+    <t>3009,1|3010,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>characterAnimatorState</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -148,9 +176,11 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -432,16 +462,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:F13"/>
+  <dimension ref="A2:G13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.625" customWidth="1"/>
     <col min="4" max="4" width="12.875" customWidth="1"/>
-    <col min="5" max="5" width="19.125" customWidth="1"/>
-    <col min="6" max="6" width="76.875" style="1" customWidth="1"/>
+    <col min="5" max="6" width="19.125" customWidth="1"/>
+    <col min="7" max="7" width="76.875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -457,11 +487,14 @@
       <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -477,11 +510,14 @@
       <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>5001</v>
       </c>
@@ -492,16 +528,19 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F4">
+        <v>-1</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>5002</v>
       </c>
@@ -512,16 +551,19 @@
         <v>0</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E5">
         <v>10</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F5">
+        <v>-1</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5003</v>
       </c>
@@ -532,16 +574,19 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E6">
         <v>10</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F6">
+        <v>-1</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5004</v>
       </c>
@@ -552,40 +597,46 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E7">
         <v>10</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F7">
+        <v>-1</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>5005</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="E8">
         <v>10</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F8">
+        <v>-1</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>5006</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C9">
@@ -597,15 +648,18 @@
       <c r="E9">
         <v>10</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F9">
+        <v>-1</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>5007</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C10">
@@ -617,15 +671,18 @@
       <c r="E10">
         <v>10</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F10">
+        <v>-1</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>5008</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
       <c r="C11">
@@ -637,15 +694,18 @@
       <c r="E11">
         <v>10</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F11">
+        <v>-1</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>5009</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>19</v>
       </c>
       <c r="C12">
@@ -657,15 +717,18 @@
       <c r="E12">
         <v>10</v>
       </c>
-      <c r="F12" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F12">
+        <v>-1</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>5010</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C13">
@@ -677,7 +740,10 @@
       <c r="E13">
         <v>10</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13">
+        <v>-1</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -686,4 +752,145 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="D1:F13"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D1">
+        <v>3120</v>
+      </c>
+      <c r="E1" t="str">
+        <f>D1&amp;","&amp;0</f>
+        <v>3120,0</v>
+      </c>
+      <c r="F1" s="2"/>
+    </row>
+    <row r="2" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D2">
+        <v>3121</v>
+      </c>
+      <c r="E2" t="str">
+        <f t="shared" ref="E2:E13" si="0">E1&amp;"|"&amp;D2&amp;","&amp;0</f>
+        <v>3120,0|3121,0</v>
+      </c>
+      <c r="F2" s="2"/>
+    </row>
+    <row r="3" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D3">
+        <v>3122</v>
+      </c>
+      <c r="E3" t="str">
+        <f t="shared" si="0"/>
+        <v>3120,0|3121,0|3122,0</v>
+      </c>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D4">
+        <v>3123</v>
+      </c>
+      <c r="E4" t="str">
+        <f t="shared" si="0"/>
+        <v>3120,0|3121,0|3122,0|3123,0</v>
+      </c>
+      <c r="F4" s="2"/>
+    </row>
+    <row r="5" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D5">
+        <v>3124</v>
+      </c>
+      <c r="E5" t="str">
+        <f t="shared" si="0"/>
+        <v>3120,0|3121,0|3122,0|3123,0|3124,0</v>
+      </c>
+      <c r="F5" s="2"/>
+    </row>
+    <row r="6" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D6">
+        <v>3125</v>
+      </c>
+      <c r="E6" t="str">
+        <f t="shared" si="0"/>
+        <v>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D7">
+        <v>3126</v>
+      </c>
+      <c r="E7" t="str">
+        <f t="shared" si="0"/>
+        <v>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0|3126,0</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D8">
+        <v>3127</v>
+      </c>
+      <c r="E8" t="str">
+        <f t="shared" si="0"/>
+        <v>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0|3126,0|3127,0</v>
+      </c>
+      <c r="F8" s="2"/>
+    </row>
+    <row r="9" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D9">
+        <v>3129</v>
+      </c>
+      <c r="E9" t="str">
+        <f t="shared" si="0"/>
+        <v>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0|3126,0|3127,0|3129,0</v>
+      </c>
+      <c r="F9" s="2"/>
+    </row>
+    <row r="10" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D10">
+        <v>3137</v>
+      </c>
+      <c r="E10" t="str">
+        <f t="shared" si="0"/>
+        <v>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0|3126,0|3127,0|3129,0|3137,0</v>
+      </c>
+      <c r="F10" s="2"/>
+    </row>
+    <row r="11" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D11">
+        <v>3138</v>
+      </c>
+      <c r="E11" t="str">
+        <f t="shared" si="0"/>
+        <v>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0|3126,0|3127,0|3129,0|3137,0|3138,0</v>
+      </c>
+      <c r="F11" s="2"/>
+    </row>
+    <row r="12" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D12">
+        <v>3140</v>
+      </c>
+      <c r="E12" t="str">
+        <f t="shared" si="0"/>
+        <v>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0|3126,0|3127,0|3129,0|3137,0|3138,0|3140,0</v>
+      </c>
+      <c r="F12" s="2"/>
+    </row>
+    <row r="13" spans="4:6" x14ac:dyDescent="0.2">
+      <c r="D13">
+        <v>3141</v>
+      </c>
+      <c r="E13" t="str">
+        <f t="shared" si="0"/>
+        <v>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0|3126,0|3127,0|3129,0|3137,0|3138,0|3140,0|3141,0</v>
+      </c>
+      <c r="F13" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Datas/ManufactureData.xlsx
+++ b/Datas/ManufactureData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -96,10 +96,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>劈柴墩</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3011,0|3100,0|3101,0|3102,0|3103,0|3107,0|3111,0|3115,0|3116,0|3139,0|3168,0|3171,0|3174,0|3175,0|3177,0|3178,0</t>
   </si>
   <si>
@@ -124,6 +120,30 @@
   </si>
   <si>
     <t>characterAnimatorState</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>柴墩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000,1|2001,1|2002,1|2003,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>cameraOffset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4,0.22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.4,0.02</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -462,16 +482,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:G13"/>
+  <dimension ref="A2:H13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.625" customWidth="1"/>
     <col min="4" max="4" width="12.875" customWidth="1"/>
-    <col min="5" max="6" width="19.125" customWidth="1"/>
-    <col min="7" max="7" width="76.875" style="2" customWidth="1"/>
+    <col min="5" max="7" width="19.125" customWidth="1"/>
+    <col min="8" max="8" width="76.875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -488,13 +508,16 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -511,13 +534,16 @@
         <v>11</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>5001</v>
       </c>
@@ -536,11 +562,14 @@
       <c r="F4">
         <v>-1</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>5002</v>
       </c>
@@ -559,11 +588,14 @@
       <c r="F5">
         <v>-1</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5003</v>
       </c>
@@ -582,11 +614,14 @@
       <c r="F6">
         <v>-1</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5004</v>
       </c>
@@ -605,11 +640,14 @@
       <c r="F7">
         <v>-1</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G7" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>5005</v>
       </c>
@@ -628,11 +666,14 @@
       <c r="F8">
         <v>-1</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>5006</v>
       </c>
@@ -651,11 +692,14 @@
       <c r="F9">
         <v>-1</v>
       </c>
-      <c r="G9" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>5007</v>
       </c>
@@ -674,11 +718,14 @@
       <c r="F10">
         <v>-1</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>5008</v>
       </c>
@@ -697,11 +744,14 @@
       <c r="F11">
         <v>-1</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G11" t="s">
+        <v>32</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>5009</v>
       </c>
@@ -720,16 +770,19 @@
       <c r="F12">
         <v>-1</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G12" t="s">
+        <v>32</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>5010</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -741,10 +794,13 @@
         <v>10</v>
       </c>
       <c r="F13">
-        <v>-1</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="G13" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ManufactureData.xlsx
+++ b/Datas/ManufactureData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -127,10 +127,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2000,1|2001,1|2002,1|2003,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>cameraOffset</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -139,11 +135,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>0.4,0.22</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0.4,0.02</t>
+    <t>int2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>defaultCostItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>103,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>103,2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2000,1|2001,1|2003,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,-0.36</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -194,13 +210,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -482,16 +501,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:H13"/>
+  <dimension ref="A2:I13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.625" customWidth="1"/>
     <col min="4" max="4" width="12.875" customWidth="1"/>
-    <col min="5" max="7" width="19.125" customWidth="1"/>
-    <col min="8" max="8" width="76.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="19.125" customWidth="1"/>
+    <col min="6" max="6" width="19.125" style="3" customWidth="1"/>
+    <col min="7" max="8" width="19.125" customWidth="1"/>
+    <col min="9" max="9" width="76.875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -507,17 +528,20 @@
       <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" t="s">
         <v>26</v>
       </c>
-      <c r="G2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -533,17 +557,20 @@
       <c r="E3" t="s">
         <v>11</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>5001</v>
       </c>
@@ -557,19 +584,22 @@
         <v>20</v>
       </c>
       <c r="E4">
-        <v>10</v>
-      </c>
-      <c r="F4">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4">
         <v>-1</v>
       </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>5002</v>
       </c>
@@ -583,19 +613,22 @@
         <v>20</v>
       </c>
       <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5">
         <v>-1</v>
       </c>
-      <c r="G5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="H5" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5003</v>
       </c>
@@ -611,17 +644,20 @@
       <c r="E6">
         <v>10</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6">
         <v>-1</v>
       </c>
-      <c r="G6" t="s">
-        <v>32</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5004</v>
       </c>
@@ -637,17 +673,20 @@
       <c r="E7">
         <v>10</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7">
         <v>-1</v>
       </c>
-      <c r="G7" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="H7" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>5005</v>
       </c>
@@ -661,19 +700,22 @@
         <v>24</v>
       </c>
       <c r="E8">
-        <v>10</v>
-      </c>
-      <c r="F8">
+        <v>100</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8">
         <v>-1</v>
       </c>
-      <c r="G8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="H8" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>5006</v>
       </c>
@@ -689,17 +731,20 @@
       <c r="E9">
         <v>10</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9">
         <v>-1</v>
       </c>
-      <c r="G9" t="s">
-        <v>32</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H9" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>5007</v>
       </c>
@@ -715,17 +760,20 @@
       <c r="E10">
         <v>10</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10">
         <v>-1</v>
       </c>
-      <c r="G10" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H10" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>5008</v>
       </c>
@@ -739,19 +787,22 @@
         <v>10</v>
       </c>
       <c r="E11">
-        <v>10</v>
-      </c>
-      <c r="F11">
+        <v>3</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11">
         <v>-1</v>
       </c>
-      <c r="G11" t="s">
-        <v>32</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="H11" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>5009</v>
       </c>
@@ -765,19 +816,22 @@
         <v>10</v>
       </c>
       <c r="E12">
-        <v>10</v>
-      </c>
-      <c r="F12">
+        <v>2</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G12">
         <v>-1</v>
       </c>
-      <c r="G12" t="s">
-        <v>32</v>
-      </c>
-      <c r="H12" s="2" t="s">
+      <c r="H12" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>5010</v>
       </c>
@@ -791,16 +845,19 @@
         <v>10</v>
       </c>
       <c r="E13">
-        <v>10</v>
-      </c>
-      <c r="F13">
+        <v>2</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13">
         <v>1</v>
       </c>
-      <c r="G13" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>29</v>
+      <c r="H13" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ManufactureData.xlsx
+++ b/Datas/ManufactureData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -54,10 +54,6 @@
   </si>
   <si>
     <t>冷餐台</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4001,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -84,10 +80,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>纺织机</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>锻造炉</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -111,10 +103,6 @@
     <t>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0|3126,0|3127,0|3129,0|3137,0|3138,0|3140,0|3141,0</t>
   </si>
   <si>
-    <t>3009,1|3010,1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -161,6 +149,34 @@
   <si>
     <t>0,-0.36</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>缝纫机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>加工台</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>295,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3009,1|3010,1|3011,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2100,0|2101,0|2102,0|2103,0|2104,0|2105,0|2106,0|2107,0|2108,0|2109,0|2110,0|2111,0</t>
+  </si>
+  <si>
+    <t>2010,0|2011,0|2012,0</t>
+  </si>
+  <si>
+    <t>4015,0|4016,0|4017,0|4018,0|4021,0|4022,0|4023,0|4024,0|4028,0|4029,0|4030,0|4031,0|4032,0|4034,0|4035,0|4036,0|4037,0|4038,0|4039,0|4041,0|4042,0|4043,0|4044,0|4046,0|4047,0|4048,0</t>
+  </si>
+  <si>
+    <t>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0|4011,0|4012,0|4013,0|4014,0|4019,0|4020,0|4025,0|4026,0|4027,0|4033,0|4040,0|4045,0</t>
   </si>
 </sst>
 </file>
@@ -501,10 +517,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:I13"/>
+  <dimension ref="A2:I14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.625" customWidth="1"/>
+    <col min="3" max="3" width="9" customWidth="1"/>
     <col min="4" max="4" width="12.875" customWidth="1"/>
     <col min="5" max="5" width="19.125" customWidth="1"/>
     <col min="6" max="6" width="19.125" style="3" customWidth="1"/>
@@ -529,13 +546,13 @@
         <v>5</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>8</v>
@@ -555,16 +572,16 @@
         <v>4</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>3</v>
@@ -587,16 +604,16 @@
         <v>2</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G4">
         <v>-1</v>
       </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -604,7 +621,7 @@
         <v>5002</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -616,16 +633,16 @@
         <v>2</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G5">
         <v>-1</v>
       </c>
       <c r="H5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
@@ -633,7 +650,7 @@
         <v>5003</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -645,16 +662,16 @@
         <v>10</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G6">
         <v>-1</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
@@ -662,7 +679,7 @@
         <v>5004</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -674,16 +691,16 @@
         <v>10</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G7">
         <v>-1</v>
       </c>
       <c r="H7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -691,7 +708,7 @@
         <v>5005</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -703,16 +720,16 @@
         <v>100</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G8">
         <v>-1</v>
       </c>
       <c r="H8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -720,86 +737,86 @@
         <v>5006</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="E9">
         <v>10</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G9">
         <v>-1</v>
       </c>
       <c r="H9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>5007</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="E10">
         <v>10</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G10">
         <v>-1</v>
       </c>
       <c r="H10" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>5008</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G11">
         <v>-1</v>
       </c>
       <c r="H11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
@@ -807,7 +824,7 @@
         <v>5009</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -819,16 +836,16 @@
         <v>2</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G12">
         <v>-1</v>
       </c>
       <c r="H12" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
@@ -836,7 +853,7 @@
         <v>5010</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -848,16 +865,45 @@
         <v>2</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I13" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>5011</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>36</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>10</v>
+      </c>
+      <c r="E14">
+        <v>2</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14">
+        <v>-1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ManufactureData.xlsx
+++ b/Datas/ManufactureData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -155,10 +155,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>加工台</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>295,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -170,13 +166,42 @@
     <t>2100,0|2101,0|2102,0|2103,0|2104,0|2105,0|2106,0|2107,0|2108,0|2109,0|2110,0|2111,0</t>
   </si>
   <si>
-    <t>2010,0|2011,0|2012,0</t>
-  </si>
-  <si>
     <t>4015,0|4016,0|4017,0|4018,0|4021,0|4022,0|4023,0|4024,0|4028,0|4029,0|4030,0|4031,0|4032,0|4034,0|4035,0|4036,0|4037,0|4038,0|4039,0|4041,0|4042,0|4043,0|4044,0|4046,0|4047,0|4048,0</t>
   </si>
   <si>
     <t>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0|4011,0|4012,0|4013,0|4014,0|4019,0|4020,0|4025,0|4026,0|4027,0|4033,0|4040,0|4045,0</t>
+  </si>
+  <si>
+    <t>织布机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>制革机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纺线机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hideNull</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2011,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2010,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2012,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -517,19 +542,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:I14"/>
+  <dimension ref="A2:J16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.625" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
     <col min="4" max="4" width="12.875" customWidth="1"/>
-    <col min="5" max="5" width="19.125" customWidth="1"/>
-    <col min="6" max="6" width="19.125" style="3" customWidth="1"/>
-    <col min="7" max="8" width="19.125" customWidth="1"/>
-    <col min="9" max="9" width="76.875" style="2" customWidth="1"/>
+    <col min="5" max="6" width="19.125" customWidth="1"/>
+    <col min="7" max="7" width="19.125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="10.25" customWidth="1"/>
+    <col min="9" max="9" width="19.125" customWidth="1"/>
+    <col min="10" max="10" width="76.875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -545,20 +571,23 @@
       <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>23</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>27</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -574,20 +603,23 @@
       <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
         <v>24</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>5001</v>
       </c>
@@ -603,20 +635,23 @@
       <c r="E4">
         <v>2</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>-1</v>
       </c>
-      <c r="H4" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>5002</v>
       </c>
@@ -632,20 +667,23 @@
       <c r="E5">
         <v>2</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>-1</v>
       </c>
-      <c r="H5" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="2" t="s">
+      <c r="I5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5003</v>
       </c>
@@ -661,20 +699,23 @@
       <c r="E6">
         <v>10</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <v>-1</v>
       </c>
-      <c r="H6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="2" t="s">
+      <c r="I6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5004</v>
       </c>
@@ -690,20 +731,23 @@
       <c r="E7">
         <v>10</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" t="b">
+        <v>0</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>-1</v>
       </c>
-      <c r="H7" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="2" t="s">
+      <c r="I7" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>5005</v>
       </c>
@@ -719,20 +763,23 @@
       <c r="E8">
         <v>100</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>-1</v>
       </c>
-      <c r="H8" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>5006</v>
       </c>
@@ -748,20 +795,23 @@
       <c r="E9">
         <v>10</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9">
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9">
         <v>-1</v>
       </c>
-      <c r="H9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I9" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>5007</v>
       </c>
@@ -777,20 +827,23 @@
       <c r="E10">
         <v>10</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <v>-1</v>
       </c>
-      <c r="H10" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="I10" t="s">
+        <v>34</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>5008</v>
       </c>
@@ -806,20 +859,23 @@
       <c r="E11">
         <v>3</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <v>-1</v>
       </c>
-      <c r="H11" t="s">
-        <v>34</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>5009</v>
       </c>
@@ -835,20 +891,23 @@
       <c r="E12">
         <v>2</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <v>-1</v>
       </c>
-      <c r="H12" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="I12" t="s">
+        <v>34</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>5010</v>
       </c>
@@ -864,25 +923,28 @@
       <c r="E13">
         <v>2</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" t="b">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>1</v>
       </c>
-      <c r="H13" t="s">
-        <v>34</v>
-      </c>
-      <c r="I13" s="2" t="s">
+      <c r="I13" t="s">
+        <v>34</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>5011</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -893,17 +955,84 @@
       <c r="E14">
         <v>2</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>-1</v>
       </c>
-      <c r="H14" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>40</v>
+      <c r="I14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>5012</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15">
+        <v>-1</v>
+      </c>
+      <c r="I15" t="s">
+        <v>34</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>5013</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>10</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16" t="b">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16">
+        <v>-1</v>
+      </c>
+      <c r="I16" t="s">
+        <v>34</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ManufactureData.xlsx
+++ b/Datas/ManufactureData.xlsx
@@ -166,12 +166,6 @@
     <t>2100,0|2101,0|2102,0|2103,0|2104,0|2105,0|2106,0|2107,0|2108,0|2109,0|2110,0|2111,0</t>
   </si>
   <si>
-    <t>4015,0|4016,0|4017,0|4018,0|4021,0|4022,0|4023,0|4024,0|4028,0|4029,0|4030,0|4031,0|4032,0|4034,0|4035,0|4036,0|4037,0|4038,0|4039,0|4041,0|4042,0|4043,0|4044,0|4046,0|4047,0|4048,0</t>
-  </si>
-  <si>
-    <t>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0|4011,0|4012,0|4013,0|4014,0|4019,0|4020,0|4025,0|4026,0|4027,0|4033,0|4040,0|4045,0</t>
-  </si>
-  <si>
     <t>织布机</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -201,6 +195,14 @@
   </si>
   <si>
     <t>2012,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4015,0|4016,0|4017,0|4018,0|4021,0|4022,0|4023,0|4024,0|4028,0|4029,0|4030,0|4031,0|4032,0|4034,0|4035,0|4036,0|4037,0|4038,0|4039,0|4041,0|4042,0|4043,0|4044,0|4046,0|4047,0|4048,0|4049,0|4050,0|4051,0|4054,0|4055,0|4056,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0|4011,0|4012,0|4013,0|4014,0|4019,0|4020,0|4025,0|4026,0|4027,0|4033,0|4040,0|4045,0|4052,0|4053,0|4057,0</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -572,7 +574,7 @@
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>28</v>
@@ -604,7 +606,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>29</v>
@@ -811,7 +813,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>5007</v>
       </c>
@@ -840,7 +842,7 @@
         <v>34</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
@@ -872,7 +874,7 @@
         <v>34</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
@@ -944,7 +946,7 @@
         <v>5011</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -968,7 +970,7 @@
         <v>34</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
@@ -976,7 +978,7 @@
         <v>5012</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1000,7 +1002,7 @@
         <v>34</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
@@ -1008,7 +1010,7 @@
         <v>5013</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1032,7 +1034,7 @@
         <v>34</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/ManufactureData.xlsx
+++ b/Datas/ManufactureData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="52">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -204,6 +204,17 @@
   <si>
     <t>4000,0|4001,0|4002,0|4003,0|4004,0|4005,0|4006,0|4007,0|4008,0|4009,0|4010,0|4011,0|4012,0|4013,0|4014,0|4019,0|4020,0|4025,0|4026,0|4027,0|4033,0|4040,0|4045,0|4052,0|4053,0|4057,0</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>needItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>noItemTalk</t>
   </si>
 </sst>
 </file>
@@ -544,52 +555,58 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:J16"/>
+  <dimension ref="A2:L16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="16.625" customWidth="1"/>
-    <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="12.875" customWidth="1"/>
-    <col min="5" max="6" width="19.125" customWidth="1"/>
-    <col min="7" max="7" width="19.125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="10.25" customWidth="1"/>
-    <col min="9" max="9" width="19.125" customWidth="1"/>
-    <col min="10" max="10" width="76.875" style="2" customWidth="1"/>
+    <col min="2" max="4" width="16.625" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12.875" customWidth="1"/>
+    <col min="7" max="8" width="19.125" customWidth="1"/>
+    <col min="9" max="9" width="19.125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.25" customWidth="1"/>
+    <col min="11" max="11" width="19.125" customWidth="1"/>
+    <col min="12" max="12" width="76.875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="G2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s">
+      <c r="H2" t="s">
         <v>43</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H2" t="s">
+      <c r="J2" t="s">
         <v>23</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -597,443 +614,499 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J3" t="s">
         <v>24</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>5001</v>
       </c>
       <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>20</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <v>2</v>
       </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <v>-1</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" t="s">
         <v>34</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>5002</v>
       </c>
       <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>20</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <v>2</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H5">
+      <c r="J5">
         <v>-1</v>
       </c>
-      <c r="I5" t="s">
+      <c r="K5" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5003</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>22</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <v>10</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H6">
+      <c r="J6">
         <v>-1</v>
       </c>
-      <c r="I6" t="s">
+      <c r="K6" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>5004</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
       </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
       <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
         <v>23</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <v>10</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H7">
+      <c r="J7">
         <v>-1</v>
       </c>
-      <c r="I7" t="s">
+      <c r="K7" t="s">
         <v>34</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="L7" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>5005</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
+      <c r="C8" s="1"/>
       <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>24</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <v>100</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H8">
+      <c r="J8">
         <v>-1</v>
       </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="L8" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>5006</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
+      <c r="C9" s="1"/>
       <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
         <v>27</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <v>10</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H9">
+      <c r="J9">
         <v>-1</v>
       </c>
-      <c r="I9" t="s">
+      <c r="K9" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="L9" s="2" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="42.75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>5007</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
+      <c r="C10" s="1"/>
       <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
         <v>26</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <v>10</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H10">
+      <c r="J10">
         <v>-1</v>
       </c>
-      <c r="I10" t="s">
+      <c r="K10" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="L10" s="2" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>5008</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
+      <c r="C11" s="1"/>
       <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
         <v>25</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <v>3</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H11">
+      <c r="J11">
         <v>-1</v>
       </c>
-      <c r="I11" t="s">
+      <c r="K11" t="s">
         <v>34</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="L11" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>5009</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
+      <c r="C12" s="1"/>
       <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
         <v>10</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <v>2</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H12">
+      <c r="J12">
         <v>-1</v>
       </c>
-      <c r="I12" t="s">
+      <c r="K12" t="s">
         <v>34</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="L12" s="2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>5010</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
+      <c r="C13" s="1">
+        <v>2002</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3016</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
         <v>10</v>
       </c>
-      <c r="E13">
+      <c r="G13">
         <v>2</v>
       </c>
-      <c r="F13" t="b">
+      <c r="H13" t="b">
         <v>1</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="I13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H13">
+      <c r="J13">
         <v>1</v>
       </c>
-      <c r="I13" t="s">
+      <c r="K13" t="s">
         <v>34</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="L13" s="2" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>5011</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
+      <c r="C14" s="1"/>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
         <v>10</v>
       </c>
-      <c r="E14">
+      <c r="G14">
         <v>2</v>
       </c>
-      <c r="F14" t="b">
+      <c r="H14" t="b">
         <v>1</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H14">
+      <c r="J14">
         <v>-1</v>
       </c>
-      <c r="I14" t="s">
+      <c r="K14" t="s">
         <v>34</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="L14" s="2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>5012</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
+      <c r="C15" s="1"/>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
         <v>10</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <v>2</v>
       </c>
-      <c r="F15" t="b">
+      <c r="H15" t="b">
         <v>1</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="I15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H15">
+      <c r="J15">
         <v>-1</v>
       </c>
-      <c r="I15" t="s">
+      <c r="K15" t="s">
         <v>34</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="L15" s="2" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>5013</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
+      <c r="C16" s="1"/>
+      <c r="D16" s="1">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
         <v>10</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <v>2</v>
       </c>
-      <c r="F16" t="b">
+      <c r="H16" t="b">
         <v>1</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="I16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="H16">
+      <c r="J16">
         <v>-1</v>
       </c>
-      <c r="I16" t="s">
+      <c r="K16" t="s">
         <v>34</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="L16" s="2" t="s">
         <v>46</v>
       </c>
     </row>

--- a/Datas/ManufactureData.xlsx
+++ b/Datas/ManufactureData.xlsx
@@ -88,21 +88,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3011,0|3100,0|3101,0|3102,0|3103,0|3107,0|3111,0|3115,0|3116,0|3139,0|3168,0|3171,0|3174,0|3175,0|3177,0|3178,0</t>
-  </si>
-  <si>
-    <t>3104,0|3109,0|3117,0|3118,0|3132,0|3133,0|3135,0|3136,0|3166,0|3167,0|3169,0|3170,0|3172,0|3173,0|3176,0</t>
-  </si>
-  <si>
-    <t>3105,0|3106,0|3108,0|3110,0|3112,0|3113,0|3114,0|3119,0|3128,0|3131,0|3134,0|3150,0|3151,0|3152,0|3153,0|3154,0|3155,0|3156,0|3157,0|3158,0|3159,0|3160,0|3161,0|3162,0|3163,0|3164,0|3165,0</t>
-  </si>
-  <si>
-    <t>3130,0|3142,0|3143,0|3144,0|3145,0|3146,0|3147,0|3148,0|3149,0</t>
-  </si>
-  <si>
-    <t>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0|3126,0|3127,0|3129,0|3137,0|3138,0|3140,0|3141,0</t>
-  </si>
-  <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -215,6 +200,21 @@
   </si>
   <si>
     <t>noItemTalk</t>
+  </si>
+  <si>
+    <t>3013,0|3014,0|3015,0|3016,0|3020,0|3024,0|3028,0|3029,0|3052,0|3081,0|3084,0|3087,0|3088,0|3090,0|3091,0</t>
+  </si>
+  <si>
+    <t>3033,0|3034,0|3035,0|3036,0|3037,0|3038,0|3039,0|3040,0|3042,0|3012,0|3050,0|3051,0|3053,0|3054,0|3092,0</t>
+  </si>
+  <si>
+    <t>3018,0|3019,0|3021,0|3023,0|3025,0|3026,0|3027,0|3032,0|3041,0|3044,0|3047,0|3063,0|3064,0|3065,0|3066,0|3067,0|3068,0|3069,0|3070,0|3071,0|3072,0|3073,0|3074,0|3075,0|3076,0|3077,0</t>
+  </si>
+  <si>
+    <t>3017,0|3022,0|3030,0|3031,0|3045,0|3046,0|3048,0|3049,0|3078,0|3079,0|3080,0|3082,0|3083,0|3085,0|3086,0|3089,0</t>
+  </si>
+  <si>
+    <t>3043,0|3055,0|3056,0|3057,0|3058,0|3059,0|3060,0|3061,0|3062,0</t>
   </si>
 </sst>
 </file>
@@ -558,13 +558,14 @@
   <dimension ref="A2:L16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="4" width="16.625" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
-    <col min="6" max="6" width="12.875" customWidth="1"/>
-    <col min="7" max="8" width="19.125" customWidth="1"/>
-    <col min="9" max="9" width="19.125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.25" customWidth="1"/>
-    <col min="11" max="11" width="19.125" customWidth="1"/>
+    <col min="2" max="2" width="16.625" customWidth="1"/>
+    <col min="3" max="4" width="16.625" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="9" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="12.875" hidden="1" customWidth="1"/>
+    <col min="7" max="8" width="19.125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="19.125" style="3" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="10.25" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="19.125" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="76.875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -579,7 +580,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -591,16 +592,16 @@
         <v>5</v>
       </c>
       <c r="H2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="K2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>8</v>
@@ -614,10 +615,10 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -629,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="H3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>3</v>
@@ -667,19 +668,19 @@
         <v>0</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J4">
         <v>-1</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>5002</v>
       </c>
@@ -702,19 +703,19 @@
         <v>0</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J5">
         <v>-1</v>
       </c>
       <c r="K5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5003</v>
       </c>
@@ -737,16 +738,16 @@
         <v>0</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J6">
         <v>-1</v>
       </c>
       <c r="K6" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
@@ -772,16 +773,16 @@
         <v>0</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J7">
         <v>-1</v>
       </c>
       <c r="K7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -808,16 +809,16 @@
         <v>0</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J8">
         <v>-1</v>
       </c>
       <c r="K8" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
@@ -844,16 +845,16 @@
         <v>0</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="J9">
         <v>-1</v>
       </c>
       <c r="K9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="42.75" x14ac:dyDescent="0.2">
@@ -861,7 +862,7 @@
         <v>5007</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10">
@@ -880,16 +881,16 @@
         <v>0</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J10">
         <v>-1</v>
       </c>
       <c r="K10" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="28.5" x14ac:dyDescent="0.2">
@@ -916,16 +917,16 @@
         <v>0</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -952,16 +953,16 @@
         <v>0</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J12">
         <v>-1</v>
       </c>
       <c r="K12" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -969,7 +970,7 @@
         <v>5010</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C13" s="1">
         <v>2002</v>
@@ -990,16 +991,16 @@
         <v>1</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J13">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
@@ -1007,7 +1008,7 @@
         <v>5011</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1">
@@ -1026,16 +1027,16 @@
         <v>1</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J14">
         <v>-1</v>
       </c>
       <c r="K14" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
@@ -1043,7 +1044,7 @@
         <v>5012</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1">
@@ -1062,16 +1063,16 @@
         <v>1</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J15">
         <v>-1</v>
       </c>
       <c r="K15" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
@@ -1079,7 +1080,7 @@
         <v>5013</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C16" s="1"/>
       <c r="D16" s="1">
@@ -1098,16 +1099,16 @@
         <v>1</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J16">
         <v>-1</v>
       </c>
       <c r="K16" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1124,132 +1125,104 @@
   <sheetData>
     <row r="1" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D1">
-        <v>3120</v>
+        <v>3043</v>
       </c>
       <c r="E1" t="str">
         <f>D1&amp;","&amp;0</f>
-        <v>3120,0</v>
+        <v>3043,0</v>
       </c>
       <c r="F1" s="2"/>
     </row>
     <row r="2" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D2">
-        <v>3121</v>
+        <v>3055</v>
       </c>
       <c r="E2" t="str">
-        <f t="shared" ref="E2:E13" si="0">E1&amp;"|"&amp;D2&amp;","&amp;0</f>
-        <v>3120,0|3121,0</v>
+        <f t="shared" ref="E2:E26" si="0">E1&amp;"|"&amp;D2&amp;","&amp;0</f>
+        <v>3043,0|3055,0</v>
       </c>
       <c r="F2" s="2"/>
     </row>
     <row r="3" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D3">
-        <v>3122</v>
+        <v>3056</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" si="0"/>
-        <v>3120,0|3121,0|3122,0</v>
+        <v>3043,0|3055,0|3056,0</v>
       </c>
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D4">
-        <v>3123</v>
+        <v>3057</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
-        <v>3120,0|3121,0|3122,0|3123,0</v>
+        <v>3043,0|3055,0|3056,0|3057,0</v>
       </c>
       <c r="F4" s="2"/>
     </row>
     <row r="5" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D5">
-        <v>3124</v>
+        <v>3058</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
-        <v>3120,0|3121,0|3122,0|3123,0|3124,0</v>
+        <v>3043,0|3055,0|3056,0|3057,0|3058,0</v>
       </c>
       <c r="F5" s="2"/>
     </row>
     <row r="6" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D6">
-        <v>3125</v>
+        <v>3059</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
-        <v>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0</v>
+        <v>3043,0|3055,0|3056,0|3057,0|3058,0|3059,0</v>
       </c>
       <c r="F6" s="2"/>
     </row>
     <row r="7" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D7">
-        <v>3126</v>
+        <v>3060</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
-        <v>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0|3126,0</v>
+        <v>3043,0|3055,0|3056,0|3057,0|3058,0|3059,0|3060,0</v>
       </c>
       <c r="F7" s="2"/>
     </row>
     <row r="8" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D8">
-        <v>3127</v>
+        <v>3061</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
-        <v>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0|3126,0|3127,0</v>
+        <v>3043,0|3055,0|3056,0|3057,0|3058,0|3059,0|3060,0|3061,0</v>
       </c>
       <c r="F8" s="2"/>
     </row>
     <row r="9" spans="4:6" x14ac:dyDescent="0.2">
       <c r="D9">
-        <v>3129</v>
+        <v>3062</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
-        <v>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0|3126,0|3127,0|3129,0</v>
+        <v>3043,0|3055,0|3056,0|3057,0|3058,0|3059,0|3060,0|3061,0|3062,0</v>
       </c>
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D10">
-        <v>3137</v>
-      </c>
-      <c r="E10" t="str">
-        <f t="shared" si="0"/>
-        <v>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0|3126,0|3127,0|3129,0|3137,0</v>
-      </c>
       <c r="F10" s="2"/>
     </row>
     <row r="11" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D11">
-        <v>3138</v>
-      </c>
-      <c r="E11" t="str">
-        <f t="shared" si="0"/>
-        <v>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0|3126,0|3127,0|3129,0|3137,0|3138,0</v>
-      </c>
       <c r="F11" s="2"/>
     </row>
     <row r="12" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D12">
-        <v>3140</v>
-      </c>
-      <c r="E12" t="str">
-        <f t="shared" si="0"/>
-        <v>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0|3126,0|3127,0|3129,0|3137,0|3138,0|3140,0</v>
-      </c>
       <c r="F12" s="2"/>
     </row>
     <row r="13" spans="4:6" x14ac:dyDescent="0.2">
-      <c r="D13">
-        <v>3141</v>
-      </c>
-      <c r="E13" t="str">
-        <f t="shared" si="0"/>
-        <v>3120,0|3121,0|3122,0|3123,0|3124,0|3125,0|3126,0|3127,0|3129,0|3137,0|3138,0|3140,0|3141,0</v>
-      </c>
       <c r="F13" s="2"/>
     </row>
   </sheetData>

--- a/Datas/ManufactureData.xlsx
+++ b/Datas/ManufactureData.xlsx
@@ -1138,7 +1138,7 @@
         <v>3055</v>
       </c>
       <c r="E2" t="str">
-        <f t="shared" ref="E2:E26" si="0">E1&amp;"|"&amp;D2&amp;","&amp;0</f>
+        <f t="shared" ref="E2:E9" si="0">E1&amp;"|"&amp;D2&amp;","&amp;0</f>
         <v>3043,0|3055,0</v>
       </c>
       <c r="F2" s="2"/>

--- a/Datas/ManufactureData.xlsx
+++ b/Datas/ManufactureData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -215,6 +215,22 @@
   </si>
   <si>
     <t>3043,0|3055,0|3056,0|3057,0|3058,0|3059,0|3060,0|3061,0|3062,0</t>
+  </si>
+  <si>
+    <t>纺织机</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2011,1|2012,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高温炉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2020,1|2021,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -555,7 +571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:L16"/>
+  <dimension ref="A2:L18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.625" customWidth="1"/>
@@ -1111,6 +1127,28 @@
         <v>41</v>
       </c>
     </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>5014</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>5015</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/ManufactureData.xlsx
+++ b/Datas/ManufactureData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="56">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -574,14 +574,13 @@
   <dimension ref="A2:L18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="16.625" customWidth="1"/>
-    <col min="3" max="4" width="16.625" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="9" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="12.875" hidden="1" customWidth="1"/>
-    <col min="7" max="8" width="19.125" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="19.125" style="3" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="10.25" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="19.125" hidden="1" customWidth="1"/>
+    <col min="2" max="4" width="16.625" customWidth="1"/>
+    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12.875" customWidth="1"/>
+    <col min="7" max="8" width="19.125" customWidth="1"/>
+    <col min="9" max="9" width="19.125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.25" customWidth="1"/>
+    <col min="11" max="11" width="19.125" customWidth="1"/>
     <col min="12" max="12" width="76.875" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -675,7 +674,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -710,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -745,7 +744,7 @@
         <v>0</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -780,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -816,7 +815,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G8">
         <v>100</v>
@@ -960,7 +959,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -998,7 +997,7 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1034,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="F14">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1070,7 +1069,7 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1106,7 +1105,7 @@
         <v>0</v>
       </c>
       <c r="F16">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1134,6 +1133,30 @@
       <c r="B17" s="1" t="s">
         <v>52</v>
       </c>
+      <c r="D17" s="1">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>2</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17">
+        <v>-1</v>
+      </c>
+      <c r="K17" t="s">
+        <v>29</v>
+      </c>
       <c r="L17" s="2" t="s">
         <v>53</v>
       </c>
@@ -1144,6 +1167,30 @@
       </c>
       <c r="B18" s="1" t="s">
         <v>54</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18">
+        <v>-1</v>
+      </c>
+      <c r="K18" t="s">
+        <v>29</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>55</v>
